--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -31711,7 +31711,7 @@
         <v>136336941</v>
       </c>
       <c r="B268" t="n">
-        <v>99364</v>
+        <v>99367</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -31711,7 +31711,7 @@
         <v>136336941</v>
       </c>
       <c r="B268" t="n">
-        <v>99367</v>
+        <v>99368</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -9234,7 +9234,7 @@
         <v>136336934</v>
       </c>
       <c r="B75" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136336942</v>
       </c>
       <c r="B106" t="n">
-        <v>79553</v>
+        <v>79555</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>136336929</v>
       </c>
       <c r="B199" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>136336930</v>
       </c>
       <c r="B200" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>136336936</v>
       </c>
       <c r="B201" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>136336937</v>
       </c>
       <c r="B202" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>136336938</v>
       </c>
       <c r="B203" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>136336943</v>
       </c>
       <c r="B204" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>136336947</v>
       </c>
       <c r="B205" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>136336949</v>
       </c>
       <c r="B206" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>136336950</v>
       </c>
       <c r="B207" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>136336951</v>
       </c>
       <c r="B208" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>136336955</v>
       </c>
       <c r="B209" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>136336958</v>
       </c>
       <c r="B210" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>136336961</v>
       </c>
       <c r="B211" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>136336963</v>
       </c>
       <c r="B212" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>136336964</v>
       </c>
       <c r="B213" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>136336968</v>
       </c>
       <c r="B214" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>136336940</v>
       </c>
       <c r="B220" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>136336952</v>
       </c>
       <c r="B221" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>136336959</v>
       </c>
       <c r="B222" t="n">
-        <v>83461</v>
+        <v>83463</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>136336932</v>
       </c>
       <c r="B223" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>136336956</v>
       </c>
       <c r="B224" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -28389,7 +28389,7 @@
         <v>136336944</v>
       </c>
       <c r="B240" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28506,7 +28506,7 @@
         <v>136336945</v>
       </c>
       <c r="B241" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -29110,7 +29110,7 @@
         <v>136336935</v>
       </c>
       <c r="B246" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>136336941</v>
       </c>
       <c r="B268" t="n">
-        <v>99368</v>
+        <v>99373</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>136336931</v>
       </c>
       <c r="B271" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>136336939</v>
       </c>
       <c r="B272" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>136336948</v>
       </c>
       <c r="B273" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>136336954</v>
       </c>
       <c r="B274" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>136336960</v>
       </c>
       <c r="B275" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>136336965</v>
       </c>
       <c r="B276" t="n">
-        <v>78483</v>
+        <v>78485</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -31711,7 +31711,7 @@
         <v>136336941</v>
       </c>
       <c r="B268" t="n">
-        <v>99373</v>
+        <v>99375</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -9234,7 +9234,7 @@
         <v>136336934</v>
       </c>
       <c r="B75" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136336942</v>
       </c>
       <c r="B106" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>136336929</v>
       </c>
       <c r="B199" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>136336930</v>
       </c>
       <c r="B200" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>136336936</v>
       </c>
       <c r="B201" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>136336937</v>
       </c>
       <c r="B202" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>136336938</v>
       </c>
       <c r="B203" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>136336943</v>
       </c>
       <c r="B204" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>136336947</v>
       </c>
       <c r="B205" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>136336949</v>
       </c>
       <c r="B206" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>136336950</v>
       </c>
       <c r="B207" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>136336951</v>
       </c>
       <c r="B208" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>136336955</v>
       </c>
       <c r="B209" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>136336958</v>
       </c>
       <c r="B210" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>136336961</v>
       </c>
       <c r="B211" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>136336963</v>
       </c>
       <c r="B212" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>136336964</v>
       </c>
       <c r="B213" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>136336968</v>
       </c>
       <c r="B214" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>136336940</v>
       </c>
       <c r="B220" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>136336952</v>
       </c>
       <c r="B221" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>136336959</v>
       </c>
       <c r="B222" t="n">
-        <v>83463</v>
+        <v>83467</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>136336932</v>
       </c>
       <c r="B223" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>136336956</v>
       </c>
       <c r="B224" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>136336941</v>
       </c>
       <c r="B268" t="n">
-        <v>99375</v>
+        <v>99381</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>

--- a/artfynd/Svanvik SO avvanm artfynd.xlsx
+++ b/artfynd/Svanvik SO avvanm artfynd.xlsx
@@ -9234,7 +9234,7 @@
         <v>136336934</v>
       </c>
       <c r="B75" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>136336942</v>
       </c>
       <c r="B106" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>136336929</v>
       </c>
       <c r="B199" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>136336930</v>
       </c>
       <c r="B200" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23854,7 +23854,7 @@
         <v>136336936</v>
       </c>
       <c r="B201" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>136336937</v>
       </c>
       <c r="B202" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24078,7 +24078,7 @@
         <v>136336938</v>
       </c>
       <c r="B203" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>136336943</v>
       </c>
       <c r="B204" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24307,7 +24307,7 @@
         <v>136336947</v>
       </c>
       <c r="B205" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>136336949</v>
       </c>
       <c r="B206" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24531,7 +24531,7 @@
         <v>136336950</v>
       </c>
       <c r="B207" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>136336951</v>
       </c>
       <c r="B208" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24760,7 +24760,7 @@
         <v>136336955</v>
       </c>
       <c r="B209" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24872,7 +24872,7 @@
         <v>136336958</v>
       </c>
       <c r="B210" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>136336961</v>
       </c>
       <c r="B211" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>136336963</v>
       </c>
       <c r="B212" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>136336964</v>
       </c>
       <c r="B213" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25325,7 +25325,7 @@
         <v>136336968</v>
       </c>
       <c r="B214" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -26022,7 +26022,7 @@
         <v>136336940</v>
       </c>
       <c r="B220" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>136336952</v>
       </c>
       <c r="B221" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>136336959</v>
       </c>
       <c r="B222" t="n">
-        <v>83467</v>
+        <v>83469</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26358,7 +26358,7 @@
         <v>136336932</v>
       </c>
       <c r="B223" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>136336956</v>
       </c>
       <c r="B224" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -31711,7 +31711,7 @@
         <v>136336941</v>
       </c>
       <c r="B268" t="n">
-        <v>99381</v>
+        <v>99383</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -32060,7 +32060,7 @@
         <v>136336931</v>
       </c>
       <c r="B271" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>136336939</v>
       </c>
       <c r="B272" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32284,7 +32284,7 @@
         <v>136336948</v>
       </c>
       <c r="B273" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32396,7 +32396,7 @@
         <v>136336954</v>
       </c>
       <c r="B274" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32508,7 +32508,7 @@
         <v>136336960</v>
       </c>
       <c r="B275" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>136336965</v>
       </c>
       <c r="B276" t="n">
-        <v>78485</v>
+        <v>78487</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
